--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF100EF-9CA9-4BCD-A31E-CEC294EDAD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7352EC-0289-4D07-BF08-0DA67A4ABCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5685"/>
+  <dimension ref="A1:E5687"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97102,6 +97102,40 @@
         <v>6332</v>
       </c>
     </row>
+    <row r="5686" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5686">
+        <v>618426</v>
+      </c>
+      <c r="B5686">
+        <v>20260912</v>
+      </c>
+      <c r="C5686" s="1">
+        <v>8735</v>
+      </c>
+      <c r="D5686" s="1">
+        <v>237</v>
+      </c>
+      <c r="E5686" s="1">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="5687" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5687">
+        <v>618526</v>
+      </c>
+      <c r="B5687">
+        <v>20260913</v>
+      </c>
+      <c r="C5687" s="1">
+        <v>9621</v>
+      </c>
+      <c r="D5687" s="1">
+        <v>3360</v>
+      </c>
+      <c r="E5687" s="1">
+        <v>4273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7352EC-0289-4D07-BF08-0DA67A4ABCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51109392-134E-4909-B8B5-A48DDABAB002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5687"/>
+  <dimension ref="A1:E5688"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97136,6 +97136,23 @@
         <v>4273</v>
       </c>
     </row>
+    <row r="5688" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5688">
+        <v>618626</v>
+      </c>
+      <c r="B5688">
+        <v>20260916</v>
+      </c>
+      <c r="C5688" s="1">
+        <v>2439</v>
+      </c>
+      <c r="D5688" s="1">
+        <v>1755</v>
+      </c>
+      <c r="E5688" s="1">
+        <v>5059</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51109392-134E-4909-B8B5-A48DDABAB002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4282C5-A8AC-43C4-AD2D-A4C8B0F65ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5688"/>
+  <dimension ref="A1:E5690"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97153,6 +97153,40 @@
         <v>5059</v>
       </c>
     </row>
+    <row r="5689" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5689">
+        <v>618726</v>
+      </c>
+      <c r="B5689">
+        <v>20260919</v>
+      </c>
+      <c r="C5689" s="1">
+        <v>6228</v>
+      </c>
+      <c r="D5689" s="1">
+        <v>2761</v>
+      </c>
+      <c r="E5689" s="1">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="5690" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5690">
+        <v>618826</v>
+      </c>
+      <c r="B5690">
+        <v>20260920</v>
+      </c>
+      <c r="C5690" s="1">
+        <v>9653</v>
+      </c>
+      <c r="D5690" s="1">
+        <v>2275</v>
+      </c>
+      <c r="E5690" s="1">
+        <v>2809</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4282C5-A8AC-43C4-AD2D-A4C8B0F65ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208DAD35-DAD1-48C9-8CE9-CCDD2A3F2770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5690"/>
+  <dimension ref="A1:E5693"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97187,6 +97187,57 @@
         <v>2809</v>
       </c>
     </row>
+    <row r="5691" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5691">
+        <v>618926</v>
+      </c>
+      <c r="B5691">
+        <v>20260923</v>
+      </c>
+      <c r="C5691" s="1">
+        <v>3715</v>
+      </c>
+      <c r="D5691" s="1">
+        <v>2740</v>
+      </c>
+      <c r="E5691" s="1">
+        <v>7599</v>
+      </c>
+    </row>
+    <row r="5692" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5692">
+        <v>619026</v>
+      </c>
+      <c r="B5692">
+        <v>20260926</v>
+      </c>
+      <c r="C5692" s="1">
+        <v>8622</v>
+      </c>
+      <c r="D5692" s="1">
+        <v>5765</v>
+      </c>
+      <c r="E5692" s="1">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="5693" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5693">
+        <v>619126</v>
+      </c>
+      <c r="B5693">
+        <v>20260927</v>
+      </c>
+      <c r="C5693" s="1">
+        <v>9069</v>
+      </c>
+      <c r="D5693" s="1">
+        <v>1317</v>
+      </c>
+      <c r="E5693" s="1">
+        <v>7612</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208DAD35-DAD1-48C9-8CE9-CCDD2A3F2770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F7C25C-7A2A-41AA-8A99-3F38B1A8843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5693"/>
+  <dimension ref="A1:E5696"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97238,6 +97238,57 @@
         <v>7612</v>
       </c>
     </row>
+    <row r="5694" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5694">
+        <v>619226</v>
+      </c>
+      <c r="B5694">
+        <v>20260930</v>
+      </c>
+      <c r="C5694" s="1">
+        <v>7161</v>
+      </c>
+      <c r="D5694" s="1">
+        <v>5641</v>
+      </c>
+      <c r="E5694" s="1">
+        <v>3682</v>
+      </c>
+    </row>
+    <row r="5695" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5695">
+        <v>619326</v>
+      </c>
+      <c r="B5695">
+        <v>20261003</v>
+      </c>
+      <c r="C5695" s="1">
+        <v>9728</v>
+      </c>
+      <c r="D5695" s="1">
+        <v>8870</v>
+      </c>
+      <c r="E5695" s="1">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="5696" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5696">
+        <v>619426</v>
+      </c>
+      <c r="B5696">
+        <v>20261004</v>
+      </c>
+      <c r="C5696" s="1">
+        <v>7175</v>
+      </c>
+      <c r="D5696" s="1">
+        <v>2014</v>
+      </c>
+      <c r="E5696" s="1">
+        <v>453</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F7C25C-7A2A-41AA-8A99-3F38B1A8843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC25A5DD-2E0F-4962-8213-768FE08ADD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5696"/>
+  <dimension ref="A1:E5697"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97289,6 +97289,23 @@
         <v>453</v>
       </c>
     </row>
+    <row r="5697" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5697">
+        <v>619526</v>
+      </c>
+      <c r="B5697">
+        <v>20261007</v>
+      </c>
+      <c r="C5697" s="1">
+        <v>2723</v>
+      </c>
+      <c r="D5697" s="1">
+        <v>857</v>
+      </c>
+      <c r="E5697" s="1">
+        <v>3034</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC25A5DD-2E0F-4962-8213-768FE08ADD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5715D0AB-4763-4A7D-861E-EE86B0519FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5697"/>
+  <dimension ref="A1:E5699"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97306,6 +97306,40 @@
         <v>3034</v>
       </c>
     </row>
+    <row r="5698" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5698">
+        <v>619626</v>
+      </c>
+      <c r="B5698">
+        <v>20261010</v>
+      </c>
+      <c r="C5698" s="1">
+        <v>1236</v>
+      </c>
+      <c r="D5698" s="1">
+        <v>4164</v>
+      </c>
+      <c r="E5698" s="1">
+        <v>9069</v>
+      </c>
+    </row>
+    <row r="5699" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5699">
+        <v>619726</v>
+      </c>
+      <c r="B5699">
+        <v>20261011</v>
+      </c>
+      <c r="C5699" s="1">
+        <v>2224</v>
+      </c>
+      <c r="D5699" s="1">
+        <v>2149</v>
+      </c>
+      <c r="E5699" s="1">
+        <v>3561</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5715D0AB-4763-4A7D-861E-EE86B0519FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE9EEB4-30A9-4CC9-BFFA-565629FEEA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5699"/>
+  <dimension ref="A1:E5700"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97340,6 +97340,23 @@
         <v>3561</v>
       </c>
     </row>
+    <row r="5700" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5700">
+        <v>619826</v>
+      </c>
+      <c r="B5700">
+        <v>20261014</v>
+      </c>
+      <c r="C5700" s="1">
+        <v>9332</v>
+      </c>
+      <c r="D5700" s="1">
+        <v>305</v>
+      </c>
+      <c r="E5700" s="1">
+        <v>606</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE9EEB4-30A9-4CC9-BFFA-565629FEEA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61180C8B-4316-410A-985A-19DC13C31D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5700"/>
+  <dimension ref="A1:E5701"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97357,6 +97357,23 @@
         <v>606</v>
       </c>
     </row>
+    <row r="5701" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5701">
+        <v>619926</v>
+      </c>
+      <c r="B5701">
+        <v>20261017</v>
+      </c>
+      <c r="C5701" s="1">
+        <v>1508</v>
+      </c>
+      <c r="D5701" s="1">
+        <v>5241</v>
+      </c>
+      <c r="E5701" s="1">
+        <v>6336</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61180C8B-4316-410A-985A-19DC13C31D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD82431-2BB3-4013-B232-EE13CE5C3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5701"/>
+  <dimension ref="A1:E5702"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97374,6 +97374,23 @@
         <v>6336</v>
       </c>
     </row>
+    <row r="5702" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5702">
+        <v>620026</v>
+      </c>
+      <c r="B5702">
+        <v>20261018</v>
+      </c>
+      <c r="C5702" s="1">
+        <v>3166</v>
+      </c>
+      <c r="D5702" s="1">
+        <v>6640</v>
+      </c>
+      <c r="E5702" s="1">
+        <v>4937</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD82431-2BB3-4013-B232-EE13CE5C3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1458F82-AEFE-4931-8AC2-4A8535CC886F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5702"/>
+  <dimension ref="A1:E5703"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97391,6 +97391,23 @@
         <v>4937</v>
       </c>
     </row>
+    <row r="5703" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5703">
+        <v>620126</v>
+      </c>
+      <c r="B5703">
+        <v>20261021</v>
+      </c>
+      <c r="C5703" s="1">
+        <v>5915</v>
+      </c>
+      <c r="D5703" s="1">
+        <v>4831</v>
+      </c>
+      <c r="E5703" s="1">
+        <v>4246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1458F82-AEFE-4931-8AC2-4A8535CC886F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D69C7D3-5DD2-456B-95F4-04539AC3C5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5703"/>
+  <dimension ref="A1:E5705"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97408,6 +97408,40 @@
         <v>4246</v>
       </c>
     </row>
+    <row r="5704" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5704">
+        <v>620226</v>
+      </c>
+      <c r="B5704">
+        <v>20261024</v>
+      </c>
+      <c r="C5704" s="1">
+        <v>7820</v>
+      </c>
+      <c r="D5704" s="1">
+        <v>2922</v>
+      </c>
+      <c r="E5704" s="1">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="5705" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5705">
+        <v>620326</v>
+      </c>
+      <c r="B5705">
+        <v>20261025</v>
+      </c>
+      <c r="C5705" s="1">
+        <v>6298</v>
+      </c>
+      <c r="D5705" s="1">
+        <v>6271</v>
+      </c>
+      <c r="E5705" s="1">
+        <v>637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D69C7D3-5DD2-456B-95F4-04539AC3C5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E45786-96DC-4565-A53C-8EA40A2A81CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5705"/>
+  <dimension ref="A1:E5706"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97442,6 +97442,23 @@
         <v>637</v>
       </c>
     </row>
+    <row r="5706" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5706">
+        <v>620426</v>
+      </c>
+      <c r="B5706">
+        <v>20261027</v>
+      </c>
+      <c r="C5706" s="1">
+        <v>9241</v>
+      </c>
+      <c r="D5706" s="1">
+        <v>6818</v>
+      </c>
+      <c r="E5706" s="1">
+        <v>4768</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E45786-96DC-4565-A53C-8EA40A2A81CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5070F3-9D25-411D-A29C-70272244D477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5706"/>
+  <dimension ref="A1:E5707"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97459,6 +97459,23 @@
         <v>4768</v>
       </c>
     </row>
+    <row r="5707" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5707">
+        <v>620526</v>
+      </c>
+      <c r="B5707">
+        <v>20261028</v>
+      </c>
+      <c r="C5707" s="1">
+        <v>7986</v>
+      </c>
+      <c r="D5707" s="1">
+        <v>3692</v>
+      </c>
+      <c r="E5707" s="1">
+        <v>4564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TotoHistoryAll.xlsx
+++ b/TotoHistoryAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5070F3-9D25-411D-A29C-70272244D477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71419255-21F0-4D10-8C96-A46A69F0E521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{4E652FB8-A0C2-4A28-A914-3B76C982BB3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E26EED-1AA9-4D18-9D07-CFB9A717AE8A}">
-  <dimension ref="A1:E5707"/>
+  <dimension ref="A1:E5708"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
@@ -97476,6 +97476,23 @@
         <v>4564</v>
       </c>
     </row>
+    <row r="5708" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5708">
+        <v>620626</v>
+      </c>
+      <c r="B5708">
+        <v>20261031</v>
+      </c>
+      <c r="C5708" s="1">
+        <v>878</v>
+      </c>
+      <c r="D5708" s="1">
+        <v>2783</v>
+      </c>
+      <c r="E5708" s="1">
+        <v>1789</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
